--- a/diseases/d140/2026-2029.xlsx
+++ b/diseases/d140/2026-2029.xlsx
@@ -12868,6 +12868,151 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>mycoplasma-pneumonia</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>支原体肺炎</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>195</v>
+      </c>
+      <c r="O72" t="n">
+        <v>195</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0.1592776394753244</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12901,7 +13046,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12984,7 +13129,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -12994,7 +13139,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
@@ -13046,7 +13191,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4617</v>
+        <v>4812</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d140/2026-2029.xlsx
+++ b/diseases/d140/2026-2029.xlsx
@@ -13013,6 +13013,151 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>mycoplasma-pneumonia</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>支原体肺炎</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>193</v>
+      </c>
+      <c r="O73" t="n">
+        <v>193</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0.1576440226601929</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13046,7 +13191,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13274,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -13139,7 +13284,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
@@ -13191,7 +13336,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4812</v>
+        <v>5005</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d140/2026-2029.xlsx
+++ b/diseases/d140/2026-2029.xlsx
@@ -13158,6 +13158,151 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>mycoplasma-pneumonia</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>支原体肺炎</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>210</v>
+      </c>
+      <c r="O74" t="n">
+        <v>210</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.1715297655888109</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13191,7 +13336,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13274,7 +13419,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
@@ -13284,7 +13429,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -13336,7 +13481,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5005</v>
+        <v>5215</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d140/2026-2029.xlsx
+++ b/diseases/d140/2026-2029.xlsx
@@ -13303,6 +13303,151 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>mycoplasma-pneumonia</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>支原体肺炎</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>263</v>
+      </c>
+      <c r="O75" t="n">
+        <v>263</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0.2148206111897965</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13336,7 +13481,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -13419,7 +13564,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -13429,7 +13574,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
@@ -13481,7 +13626,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5215</v>
+        <v>5478</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d140/2026-2029.xlsx
+++ b/diseases/d140/2026-2029.xlsx
@@ -13448,6 +13448,151 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>mycoplasma-pneumonia</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>支原体肺炎</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>247</v>
+      </c>
+      <c r="O76" t="n">
+        <v>247</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.2017516766687443</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13481,7 +13626,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -13564,7 +13709,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -13574,7 +13719,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11">
@@ -13626,7 +13771,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5478</v>
+        <v>5725</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d140/2026-2029.xlsx
+++ b/diseases/d140/2026-2029.xlsx
@@ -21972,6 +21972,151 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>mycoplasma-pneumonia</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>支原体肺炎</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>305</v>
+      </c>
+      <c r="O119" t="n">
+        <v>305</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.2491265643075587</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22005,7 +22150,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -22088,7 +22233,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -22098,7 +22243,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11">
@@ -22150,7 +22295,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5741</v>
+        <v>6046</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d140/2026-2029.xlsx
+++ b/diseases/d140/2026-2029.xlsx
@@ -22117,6 +22117,405 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>mycoplasma-pneumonia</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>支原体肺炎</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>1</v>
+      </c>
+      <c r="O120" t="n">
+        <v>1</v>
+      </c>
+      <c r="P120" t="n">
+        <v>1</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.2485528013143472</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_RESPIRATORY_MYCO_PNEUMONIA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_RESPIRATORY_MYCO_PNEUMONIA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>mycoplasma-pneumonia</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>支原体肺炎</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>1</v>
+      </c>
+      <c r="O121" t="n">
+        <v>1</v>
+      </c>
+      <c r="P121" t="n">
+        <v>1</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_RESPIRATORY_MYCO_PNEUMONIA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_RESPIRATORY_MYCO_PNEUMONIA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_RESPIRATORY</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>mycoplasma</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>clinical_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>physician_reported_clinical_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>IS_DOH_respiratory_current</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>National ISO-week physician-reported clinical Mycoplasma pneumoniae diagnoses, whether or not laboratory confirmed; this is not a statutory notification total.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_RESPIRATORY_MYCO_PNEUMONIA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22150,7 +22549,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -22233,7 +22632,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -22243,7 +22642,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
@@ -22263,7 +22662,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -22295,7 +22694,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6046</v>
+        <v>6047</v>
       </c>
     </row>
     <row r="16">
